--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -916,7 +916,7 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t># ---- bottom slab haunch : 1,050 at the web -&gt; 800 over a 1,750 run ----</t>
+          <t># ---- bottom slab haunch : one step, 1,050 at the web -&gt; 800 over a 1,750 run ----</t>
         </is>
       </c>
       <c r="C40" s="2" t="n"/>
@@ -948,7 +948,12 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>925</v>
+        <v>800</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>same as TBS — the haunch ends here</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -963,7 +968,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>875</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="44">
@@ -978,7 +983,12 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>875</v>
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>one-step haunch: the second run is not used</t>
+        </is>
       </c>
     </row>
     <row r="45">

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -845,7 +845,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t># ---- top slab haunch : 600 at the web -&gt; 280 over a 1,750 run ----</t>
+          <t># ---- top slab haunch : one step, 600 at the web -&gt; 280 over a 1,750 run ----</t>
         </is>
       </c>
       <c r="C34" s="2" t="n"/>
@@ -877,7 +877,12 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>440</v>
+        <v>280</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>same as TTS — the haunch ends here</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -892,7 +897,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>875</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="38">
@@ -907,7 +912,12 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>875</v>
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>one-step haunch: the second run is not used</t>
+        </is>
       </c>
     </row>
     <row r="39">

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -50,12 +50,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,20 +422,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1146,13 +1150,300 @@
     <row r="57">
       <c r="C57" s="2" t="n"/>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t># ---- rebar : 상부슬래브 + 좌우 캔틸레버 H13 (주두부 배근도(2) / 8-244) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t># trebar | id | code | dia | init x,y,rot | set | segs | angs | nors | end:start | end:end | radius | z</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>#   code 1 = 직선(A) · 11 = ㄱ자(A→B). angs 의 a 는 A 다음 꺾임각이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>#   set 은 벽 id — E1/E2 데크 상면, E12·E13 좌측 캔틸레버 하면, E5·E4 우측 캔틸레버 하면</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>#   꺾임각 88.282 / 91.718 은 데크 -3% 경사에 대해 다리가 연직이라는 뜻이다 (90 ∓ 1.718)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>#   세그먼트는 도면 그림 순서대로 — 자유단(190 다리)에서 안쪽으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>#   N=33 은 교축방향 개수(세그먼트 18,000 에 ctc 약 550)라 이 블록에는 안 들어간다</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>11</v>
+      </c>
+      <c r="D67" t="n">
+        <v>13</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>b:E1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>a:190,b:4800</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>a:88.282</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>deck top, left  · 190 leg at the left tip + 4,500 + 300 lap = 4,990</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>11</v>
+      </c>
+      <c r="D68" t="n">
+        <v>13</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>a:E2</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>a:7810,b:190</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>a:91.718</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>deck top, right · 300 lap + 7,510 + 190 leg at the right tip = 8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+      <c r="D69" t="n">
+        <v>13</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>b:E13</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>a:190,b:1400</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>a:91.718</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>left  cantilever soffit at the tip = 1,590</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>11</v>
+      </c>
+      <c r="D70" t="n">
+        <v>13</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>a:E4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>a:1400,b:190</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>a:88.282</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>right cantilever soffit at the tip = 1,590</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>13</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>a:E12</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>a:2540</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>left  cantilever soffit, straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>13</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>a:E5</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>a:2730</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>right cantilever soffit, straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -514,82 +514,64 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="2" t="n"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dia</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>격벽 두께(교축) — 폐합철근 ⑩ ⑩-1 ⑩-2 의 둘레가 이 값에서 떨어진다</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>! 페이지는 아직 dia 블록을 읽지 않는다 — 화면의 Diaphragm Length 칸에 직접 넣는다 (기본 2000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t># cover is not given on the drawings -- page defaults kept</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>cover</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B13" t="n">
         <v>50</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C13" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="12">
-      <c r="C12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="14">
+      <c r="C14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t># ---- overall ----</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Y1  deck top to soffit at centreline</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SLL</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>single -3% plane across the whole deck</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -599,11 +581,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SLR</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-3</v>
+        <v>7800</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Y1  deck top to soffit at centreline</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -614,7 +601,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SLL</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
@@ -622,7 +609,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>bottom face runs parallel to the deck</t>
+          <t>single -3% plane across the whole deck</t>
         </is>
       </c>
     </row>
@@ -634,11 +621,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TTS</t>
+          <t>SLR</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>280</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="19">
@@ -649,68 +636,63 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>bottom face runs parallel to the deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TTS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>TBS</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C21" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Y2  bottom slab at centreline</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="C20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="22">
+      <c r="C22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t># ---- widths  (right side mirrors the left) ----</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>WL</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>6200</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>12,400 / 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>WTL</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>web outer face</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -720,15 +702,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WBL</t>
+          <t>WL</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>3500</v>
+        <v>6200</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bottom slab half width, 7,000 / 2</t>
+          <t>12,400 / 2</t>
         </is>
       </c>
     </row>
@@ -740,11 +722,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WCAL1</t>
+          <t>WTL</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1750</v>
+        <v>3500</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>web outer face</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -755,11 +742,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WCAL2</t>
+          <t>WBL</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>950</v>
+        <v>3500</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>bottom slab half width, 7,000 / 2</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -770,63 +762,53 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>WCAL1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>WCAL2</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>TWEBL</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C29" s="2" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="28">
-      <c r="C28" s="2" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="30">
+      <c r="C30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t># ---- cantilever ----</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>TCAL</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>tip</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>TCAL1</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>root, at the web outer face</t>
-        </is>
-      </c>
+      <c r="C31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -836,58 +818,63 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TCAL2</t>
+          <t>TCAL</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>280</v>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>tip</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="C33" s="2" t="n"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TCAL1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>root, at the web outer face</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TCAL2</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t># ---- top slab haunch : one step, 600 at the web -&gt; 280 over a 1,750 run ----</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>TTHL1</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>TTHL2</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>same as TTS — the haunch ends here</t>
-        </is>
-      </c>
+      <c r="C36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -897,11 +884,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WTHUL1</t>
+          <t>TTHL1</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1750</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38">
@@ -912,63 +899,63 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>TTHL2</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>same as TTS — the haunch ends here</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>WTHUL1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>WTHUL2</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>one-step haunch: the second run is not used</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="C39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+    <row r="41">
+      <c r="C41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t># ---- bottom slab haunch : one step, 1,050 at the web -&gt; 800 over a 1,750 run ----</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>TBHL1</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>TBHL2</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>same as TBS — the haunch ends here</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -978,11 +965,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>WBHUL1</t>
+          <t>TBHL1</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1750</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="44">
@@ -993,15 +980,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>WBHUL2</t>
+          <t>TBHL2</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>one-step haunch: the second run is not used</t>
+          <t>same as TBS — the haunch ends here</t>
         </is>
       </c>
     </row>
@@ -1013,53 +1000,58 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>WBHUL1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>WBHUL2</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>one-step haunch: the second run is not used</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>TBEL</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C47" s="2" t="n">
         <v>1050</v>
       </c>
     </row>
-    <row r="46">
-      <c r="C46" s="2" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+    <row r="48">
+      <c r="C48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t># ---- fillets : the drawings have square corners ----</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>R_WTL</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>dim</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>R_WTIL</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="C49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1069,7 +1061,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>R_WBL</t>
+          <t>R_WTL</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
@@ -1077,28 +1069,42 @@
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="2" t="n"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>R_WTIL</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t># ---- diaphragm opening (8-020, section A-A) -- one opening, 1 Cell or 2 Cell alike ----</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dim</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>R_WBL</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t># open | shape | B | H | Cttx | Ctty | Ctbx | Ctby | X | Y</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t># 4.800 (deck top to opening top) + 1.500 (H) + 1.500 (opening bottom to soffit) = 7.800</t>
+          <t># ---- diaphragm opening (8-020, section A-A) -- one opening, 1 Cell or 2 Cell alike ----</t>
         </is>
       </c>
       <c r="C54" s="2" t="n"/>
@@ -1106,180 +1112,114 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
+          <t># open | shape | B | H | Cttx | Ctty | Ctbx | Ctby | X | Y</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t># 4.800 (deck top to opening top) + 1.500 (H) + 1.500 (opening bottom to soffit) = 7.800</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
           <t># Y is measured from the top of the bottom slab: 1500 - TBS 800 = 700</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="C57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>OCT</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C58" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D58" t="n">
         <v>1500</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E58" t="n">
         <v>250</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F58" t="n">
         <v>250</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G58" t="n">
         <v>250</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H58" t="n">
         <v>250</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I58" t="n">
         <v>0</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J58" t="n">
         <v>700</v>
       </c>
     </row>
-    <row r="57">
-      <c r="C57" s="2" t="n"/>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t># ---- rebar : 상부슬래브 + 좌우 캔틸레버 H13 (주두부 배근도(2) / 8-244) ----</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t># trebar | id | code | dia | init x,y,rot | set | segs | angs | nors | end:start | end:end | radius | z</t>
-        </is>
-      </c>
-    </row>
+    <row r="59">
+      <c r="C59" s="2" t="n"/>
+    </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>#   code 1 = 직선(A) · 11 = ㄱ자(A→B). angs 의 a 는 A 다음 꺾임각이다</t>
+          <t># ---- rebar : 상부슬래브 + 좌우 캔틸레버 H13 (주두부 배근도(2) / 8-244) ----</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>#   set 은 벽 id — E1/E2 데크 상면, E12·E13 좌측 캔틸레버 하면, E5·E4 우측 캔틸레버 하면</t>
+          <t># trebar | id | code | dia | init x,y,rot | set | segs | angs | nors | end:start | end:end | radius | z</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>#   꺾임각 88.282 / 91.718 은 데크 -3% 경사에 대해 다리가 연직이라는 뜻이다 (90 ∓ 1.718)</t>
+          <t>#   code 1 = 직선(A) · 11 = ㄱ자(A→B). angs 의 a 는 A 다음 꺾임각이다</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>#   세그먼트는 도면 그림 순서대로 — 자유단(190 다리)에서 안쪽으로</t>
+          <t>#   set 은 벽 id — E1/E2 데크 상면, E12·E13 좌측 캔틸레버 하면, E5·E4 우측 캔틸레버 하면</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
+          <t>#   꺾임각 88.282 / 91.718 은 데크 -3% 경사에 대해 다리가 연직이라는 뜻이다 (90 ∓ 1.718)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>#   세그먼트는 도면 그림 순서대로 — 자유단(190 다리)에서 안쪽으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
           <t>#   N=33 은 교축방향 개수(세그먼트 18,000 에 ctc 약 550)라 이 블록에는 안 들어간다</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>11</v>
-      </c>
-      <c r="D67" t="n">
-        <v>13</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>b:E1</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>a:190,b:4800</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>a:88.282</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>deck top, left  · 190 leg at the left tip + 4,500 + 300 lap = 4,990</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>11</v>
-      </c>
-      <c r="D68" t="n">
-        <v>13</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>a:E2</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>a:7810,b:190</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>a:91.718</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>deck top, right · 300 lap + 7,510 + 190 leg at the right tip = 8,000</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1231,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1302,17 +1242,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>b:E13</t>
+          <t>b:E1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>a:190,b:1400</t>
+          <t>a:190,b:4800</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>a:91.718</t>
+          <t>a:88.282</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -1320,7 +1260,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>left  cantilever soffit at the tip = 1,590</t>
+          <t>deck top, left  · 190 leg at the left tip + 4,500 + 300 lap = 4,990</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1272,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -1343,17 +1283,17 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>a:E4</t>
+          <t>a:E2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>a:1400,b:190</t>
+          <t>a:7810,b:190</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>a:88.282</t>
+          <t>a:91.718</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -1361,7 +1301,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>right cantilever soffit at the tip = 1,590</t>
+          <t>deck top, right · 300 lap + 7,510 + 190 leg at the right tip = 8,000</t>
         </is>
       </c>
     </row>
@@ -1373,23 +1313,28 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D71" t="n">
         <v>13</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>a:E12</t>
+          <t>b:E13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>a:2540</t>
+          <t>a:190,b:1400</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>a:91.718</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -1397,7 +1342,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>left  cantilever soffit, straight</t>
+          <t>left  cantilever soffit at the tip = 1,590</t>
         </is>
       </c>
     </row>
@@ -1409,23 +1354,28 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D72" t="n">
         <v>13</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>a:E5</t>
+          <t>a:E4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>a:2730</t>
+          <t>a:1400,b:190</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>a:88.282</t>
         </is>
       </c>
       <c r="M72" t="n">
@@ -1433,17 +1383,429 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>right cantilever soffit, straight</t>
+          <t>right cantilever soffit at the tip = 1,590</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>13</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>a:E12</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>a:2540</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>left  cantilever soffit, straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>13</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>a:E5</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>a:2730</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>right cantilever soffit, straight</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t># ---- crebar : 격벽 폐합철근 ⑩ ⑩-1 ⑩-2 (교축방향 · 닫힌 고리) ----</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t># 다른 철근(trebar)은 단면 평면에 눕는다. 이 셋은 그 평면과 90° 다르다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>#   격벽의 두께(교축 z)를 감아 도는 닫힌 고리다. 단면도에서는 선 하나로만 보인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t># 놓는 방법 : 높이 y 에서 격벽을 수평으로 자르면 평면이 하나 나온다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>#   그 평면의 콘크리트는 「그 높이의 단면 폭 x 격벽 두께」인 직사각형이고,</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>#   고리는 그 네 면을 피복만큼 띄우고 감는다. 세그먼트가 벽을 찾아가는 것은</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>#   지금 trebar 와 똑같다 — 평면만 90° 돌아간 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>#   그래서 폭을 적지 않는다. 높이만 주면 폭은 콘크리트가 정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t># crebar | id | dia | plane | at | set | lap | note</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>#   plane xz = 수평으로 자른 평면(가로 x · 교축 z). at = 자르는 높이 y</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>#     (단면 중심의 데크 크라운이 y=0, 위가 +)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>#   set all = 그 평면의 네 면을 모두 감는다(닫힌 고리). lap = 겹이음 길이</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t># 폭은 입력이 아니지만, 도면의 랩 포함 길이와 맞는지 보는 눈금은 된다 :</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>#   둘레 = 2 x (폭 + 두께) , 두께 2,000 일 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>#     ⑩   11,624 → 폭  3,812      ⑩-1  12,624 → 폭  4,312</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>#     ⑩-2 27,124 → 폭 11,562</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>#   셋 다 두께 2,000 에서 정수로 떨어진다 — 격벽 두께 2,000 의 뒷받침이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>#   놓고 나서 나온 폭이 이 값과 맞으면 높이 at 이 맞은 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>! 지금 페이지는 이 블록을 읽지 않는다 (trebar/lrebar 만 읽는다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>! 시험해 본 결과 (tools/plan_hoop_test.js — 엔진을 그대로 돌린 것) :</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>!   · 교축방향 평면 자체는 문제가 없다. 물리는 2D 평면 하나만 알 뿐 그것이</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>!     단면인지 수평면인지 모른다. 이 평면에 직선(code 1) · ㄱ자(11) · U자(21) 를</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>!     떨어뜨리면 전부 안착하고, 벽에서 52 = 피복 40 + 지름반 12.5 로 정확히 선다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>!   · U자(21)를 두께를 감는 크기로 주면 앞뒤 두 면과 옆면을 함께 문다</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>!     (z −948 ~ 953, 벽은 ∓1,000) — 이것이 곧 「고리에서 한 변만 빠진 것」이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>!   · 막히는 것은 닫힘 하나뿐이다. code 41(다섯 조각)은 치수를 어떻게 주든,</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>!     set 을 주든 안 주든 ASSEMBLING 에서 멈춘다. 엔진에 닫힌 형상이 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>!   → 그러므로 폐합철근은 U자(21) + 닫는 한 변으로 세우는 길이 열려 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>! at(높이)는 위 폭에서 거꾸로 짚은 값이다 — 주두부 배근도 (3)(4)(5) 로 확인해야 한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>25</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>-3800</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>300</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>⑩   기대 폭  3,812 (둘레 11,624)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>10-1</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>25</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>-5600</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>300</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>⑩-1 기대 폭  4,312 (둘레 12,624)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>25</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>-250</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>300</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>⑩-2 기대 폭 11,562 (둘레 27,124)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N112"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1617,195 +1617,230 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>! 지금 페이지는 이 블록을 읽지 않는다 (trebar/lrebar 만 읽는다).</t>
+          <t>! 페이지가 이 블록을 읽는다 — 높이 at 에서 격벽을 수평으로 자른 평면에 U자(21)를</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>! 시험해 본 결과 (tools/plan_hoop_test.js — 엔진을 그대로 돌린 것) :</t>
+          <t>!   안착시킨 뒤 마지막 한 변을 이어 닫는다. 3D 에 보라색으로 선다.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>!   · 교축방향 평면 자체는 문제가 없다. 물리는 2D 평면 하나만 알 뿐 그것이</t>
+          <t>! 지금 돌린 결과 : ⑩ 6,893 · ⑩-1 6,893 · ⑩-2 10,747 (감은 폭, 두께 1,901)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>!     단면인지 수평면인지 모른다. 이 평면에 직선(code 1) · ㄱ자(11) · U자(21) 를</t>
+          <t>!   ⑩ ⑩-1 이 기대폭(3,812 / 4,312)과 안 맞는다 — 그 높이의 단면 폭이 7,000 이라</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>!     떨어뜨리면 전부 안착하고, 벽에서 52 = 피복 40 + 지름반 12.5 로 정확히 선다.</t>
+          <t>! 시험해 본 결과 (tools/plan_hoop_test.js — 엔진을 그대로 돌린 것) :</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>!   · U자(21)를 두께를 감는 크기로 주면 앞뒤 두 면과 옆면을 함께 문다</t>
+          <t>!   · 교축방향 평면 자체는 문제가 없다. 물리는 2D 평면 하나만 알 뿐 그것이</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>!     (z −948 ~ 953, 벽은 ∓1,000) — 이것이 곧 「고리에서 한 변만 빠진 것」이다.</t>
+          <t>!     단면인지 수평면인지 모른다. 이 평면에 직선(code 1) · ㄱ자(11) · U자(21) 를</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>!   · 막히는 것은 닫힘 하나뿐이다. code 41(다섯 조각)은 치수를 어떻게 주든,</t>
+          <t>!     떨어뜨리면 전부 안착하고, 벽에서 52 = 피복 40 + 지름반 12.5 로 정확히 선다.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>!     set 을 주든 안 주든 ASSEMBLING 에서 멈춘다. 엔진에 닫힌 형상이 없다.</t>
+          <t>!   · U자(21)를 두께를 감는 크기로 주면 앞뒤 두 면과 옆면을 함께 문다</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>!   → 그러므로 폐합철근은 U자(21) + 닫는 한 변으로 세우는 길이 열려 있다.</t>
+          <t>!     (z −948 ~ 953, 벽은 ∓1,000) — 이것이 곧 「고리에서 한 변만 빠진 것」이다.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>! at(높이)는 위 폭에서 거꾸로 짚은 값이다 — 주두부 배근도 (3)(4)(5) 로 확인해야 한다.</t>
+          <t>!   · 막히는 것은 닫힘 하나뿐이다. code 41(다섯 조각)은 치수를 어떻게 주든,</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>25</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>-3800</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>300</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>⑩   기대 폭  3,812 (둘레 11,624)</t>
+          <t>!     set 을 주든 안 주든 ASSEMBLING 에서 멈춘다. 엔진에 닫힌 형상이 없다.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>10-1</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>25</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>-5600</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>300</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>⑩-1 기대 폭  4,312 (둘레 12,624)</t>
+          <t>!   → 그러므로 폐합철근은 U자(21) + 닫는 한 변으로 세우는 길이 열려 있다.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>10-2</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>25</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>xz</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>-250</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
-        <v>300</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>⑩-2 기대 폭 11,562 (둘레 27,124)</t>
+          <t>!   단면 전체를 감으면 6,893 이 될 수밖에 없다. 이 둘은 단면 전체가 아니라</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>!   더 좁은 무엇(복부 한 쪽·개구부 둘레 등)을 감는 고리로 보인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>!   ⑩-2 는 10,747 로 기대 11,562 에 815 모자라다 — at 을 데크 쪽으로 올리면 맞는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>25</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>-3800</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>300</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>⑩   기대 폭  3,812 (둘레 11,624)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>10-1</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>25</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>-5600</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>300</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>⑩-1 기대 폭  4,312 (둘레 12,624)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>25</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>xz</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>-250</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>300</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>⑩-2 기대 폭 11,562 (둘레 27,124)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1533,28 +1533,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t># crebar | id | dia | plane | at | set | lap | note</t>
+          <t># crebar | id | dia | plane | at | set | lap | from | to</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>#   plane xz = 수평으로 자른 평면(가로 x · 교축 z). at = 자르는 높이 y</t>
+          <t>#   plane yz = 위치 x=at 에서 세로로 자른다 → 고리의 긴 축이 수직 (도면의 ⑩ ⑩-1 ⑩-2)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>#     (단면 중심의 데크 크라운이 y=0, 위가 +)</t>
+          <t>#   plane xz = 높이 y=at 에서 수평으로 자른다 → 긴 축이 가로</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>#   set all = 그 평면의 네 면을 모두 감는다(닫힌 고리). lap = 겹이음 길이</t>
+          <t>#   set all = 그 평면의 네 면을 모두 감는다(닫힌 고리) · lap = 겹이음 · from/to = 긴 축을 잘라 쓸 때</t>
         </is>
       </c>
     </row>
@@ -1742,11 +1742,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>xz</t>
+          <t>yz</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>-3800</v>
+        <v>-1100</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -1756,9 +1756,9 @@
       <c r="G114" t="n">
         <v>300</v>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>⑩   기대 폭  3,812 (둘레 11,624)</t>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>⑩   개구부 왼쪽 · 단면 전체를 수직으로 감는다</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>10-1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -1778,11 +1778,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>xz</t>
+          <t>yz</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>-5600</v>
+        <v>1100</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -1792,9 +1792,9 @@
       <c r="G115" t="n">
         <v>300</v>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>⑩-1 기대 폭  4,312 (둘레 12,624)</t>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>⑩   개구부 오른쪽 · 좌우 한 쌍이다</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>10-2</t>
+          <t>10-1</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>xz</t>
+          <t>yz</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>-250</v>
+        <v>-300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -1828,19 +1828,61 @@
       <c r="G116" t="n">
         <v>300</v>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>⑩-2 기대 폭 11,562 (둘레 27,124)</t>
+      <c r="I116" t="n">
+        <v>-1450</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>⑩-1 개구부 아래 · 바닥에서 개구부 밑까지</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>crebar</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>25</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>yz</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>300</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>300</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-1450</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>⑩-2 개구부 아래 · 바닥에서 개구부 밑까지</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -1828,12 +1828,14 @@
       <c r="G116" t="n">
         <v>300</v>
       </c>
-      <c r="I116" t="n">
-        <v>-1450</v>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>⑩-1 개구부 아래 · 바닥에서 개구부 밑까지</t>
+          <t>⑩-1 개구부 아래 · 바닥에서 개구부 밑까지 (to:open 이 따라간다)</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1869,14 @@
       <c r="G117" t="n">
         <v>300</v>
       </c>
-      <c r="I117" t="n">
-        <v>-1450</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>⑩-2 개구부 아래 · 바닥에서 개구부 밑까지</t>
+          <t>⑩-2 개구부 아래 · 바닥에서 개구부 밑까지 (to:open 이 따라간다)</t>
         </is>
       </c>
     </row>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>a:91.718</t>
+          <t>a:-91.718</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>left  cantilever soffit at the tip = 1,590</t>
+          <t>left  cantilever soffit at the tip = 1,590 (다리 먼저 — 선단 x=-6,154 에 선다)</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>a:E4</t>
+          <t>b:E4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>a:1400,b:190</t>
+          <t>a:190,b:1400</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>right cantilever soffit at the tip = 1,590</t>
+          <t>right cantilever soffit at the tip = 1,590 (다리 먼저 — 선단 x=6,154 에 선다)</t>
         </is>
       </c>
     </row>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -1308,7 +1308,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>trebar</t>
+          <t># trebar</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>left  cantilever soffit at the tip = 1,590 (다리 먼저 — 선단 x=-6,154 에 선다)</t>
+          <t>좌측 벽 방향이 반대라 선단+안쪽이 안 된다 — 엔진 ② 넣은 뒤 되살린다</t>
         </is>
       </c>
     </row>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N118"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1533,7 +1533,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t># crebar | id | dia | plane | at | set | lap | from | to</t>
+          <t># crebar | id | dia | plane | at | set | lap | from | to | ctc</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>#   set all = 그 평면의 네 면을 모두 감는다(닫힌 고리) · lap = 겹이음 · from/to = 긴 축을 잘라 쓸 때</t>
+          <t>#   at 은 한 자리(-1100) 또는 범위(-6000~6000). 범위면 ctc 간격으로 쭉 깐다</t>
         </is>
       </c>
     </row>
@@ -1745,8 +1745,10 @@
           <t>yz</t>
         </is>
       </c>
-      <c r="E114" t="n">
-        <v>-1100</v>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-6000~6000</t>
+        </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -1756,137 +1758,22 @@
       <c r="G114" t="n">
         <v>300</v>
       </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>⑩   개구부 왼쪽 · 단면 전체를 수직으로 감는다</t>
+      <c r="J114" t="n">
+        <v>150</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>⑩ 교축직각으로 150 간격 · 단면 전체 — 개구부를 지나는 자리는 저절로 갈려 ⑩-1 ⑩-2 가 된다</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>25</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>yz</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
-        <v>300</v>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>⑩   개구부 오른쪽 · 좌우 한 쌍이다</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>10-1</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>25</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>yz</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>-300</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>300</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>⑩-1 개구부 아래 · 바닥에서 개구부 밑까지 (to:open 이 따라간다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>crebar</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>10-2</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>25</v>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>yz</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>300</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>300</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>⑩-2 개구부 아래 · 바닥에서 개구부 밑까지 (to:open 이 따라간다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -1554,7 +1554,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>#   at 은 한 자리(-1100) 또는 범위(-6000~6000). 범위면 ctc 간격으로 쭉 깐다</t>
+          <t>#   at : cell 복부 사이(기본) · all 단면 전체 · -6000~6000 범위 · -1100 한 자리</t>
         </is>
       </c>
     </row>
@@ -1740,19 +1740,9 @@
       <c r="C114" t="n">
         <v>25</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>yz</t>
-        </is>
-      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>-6000~6000</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>all</t>
+          <t>cell</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -1763,7 +1753,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>⑩ 교축직각으로 150 간격 · 단면 전체 — 개구부를 지나는 자리는 저절로 갈려 ⑩-1 ⑩-2 가 된다</t>
+          <t>⑩ 복부 사이에 150 간격 균등 — 개구부를 지나는 자리는 저절로 갈려 ⑩-1 ⑩-2 가 된다</t>
         </is>
       </c>
     </row>

--- a/PSCBOX_DIAPHRAGM_S15.xlsx
+++ b/PSCBOX_DIAPHRAGM_S15.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>좌측 벽 방향이 반대라 선단+안쪽이 안 된다 — 엔진 ② 넣은 뒤 되살린다</t>
+          <t>off for now: the left wall runs the other way, so tip+inward is not reachable. Restore once the engine can grow against the wall direction</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>right cantilever soffit at the tip = 1,590 (다리 먼저 — 선단 x=6,154 에 선다)</t>
+          <t>right cantilever soffit at the tip = 1,590 (leg first — stands at the tip, x=6,154)</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>⑩ 복부 사이에 150 간격 균등 — 개구부를 지나는 자리는 저절로 갈려 ⑩-1 ⑩-2 가 된다</t>
+          <t>hoop 10 — between the webs, 150 ctc, evenly spread. Where it crosses the opening it splits by itself into 10-1 / 10-2</t>
         </is>
       </c>
     </row>
